--- a/output/pdf_financials_xlsx/AZR.xlsx
+++ b/output/pdf_financials_xlsx/AZR.xlsx
@@ -1089,37 +1089,37 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>1.765712</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.793553</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.054948</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.011112</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.12125</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.09131599999999999</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.02628</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.001037</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000351</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.004169</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.002656</v>
       </c>
       <c r="M12" s="3" t="n">
         <v>0</v>
@@ -2141,37 +2141,37 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-7.278971</v>
+        <v>-9.044682999999999</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-15.291884</v>
+        <v>-16.085437</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-8.252311000000001</v>
+        <v>-8.307259</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-7.060448</v>
+        <v>-7.07156</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-7.280299</v>
+        <v>-7.401549</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-6.036806</v>
+        <v>-6.128122</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-9.909879999999999</v>
+        <v>-9.936159999999999</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-1.623567</v>
+        <v>-1.624604</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.688528</v>
+        <v>-0.688879</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.801061</v>
+        <v>-0.80523</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-2.574518</v>
+        <v>-2.577174</v>
       </c>
       <c r="M27" s="3" t="n">
         <v>-1.165199</v>
@@ -2269,37 +2269,37 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-7.278971</v>
+        <v>-9.044682999999999</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-15.291884</v>
+        <v>-16.085437</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-8.252311000000001</v>
+        <v>-8.307259</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-7.060448</v>
+        <v>-7.07156</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-7.280299</v>
+        <v>-7.401549</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-6.036806</v>
+        <v>-6.128122</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-9.909879999999999</v>
+        <v>-9.936159999999999</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.623567</v>
+        <v>-1.624604</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.6848070000000001</v>
+        <v>-0.685158</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.796737</v>
+        <v>-0.800906</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.574518</v>
+        <v>-2.577174</v>
       </c>
       <c r="M29" s="3" t="n">
         <v>-1.165199</v>
@@ -2628,43 +2628,43 @@
         <v>4.537174</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.679516</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.242141</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.003827</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.587046</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.036196</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.020449</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>2.599062</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.77522</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.862851</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.184074</v>
       </c>
       <c r="R34" s="3" t="n">
-        <v>0</v>
+        <v>0.123135</v>
       </c>
       <c r="S34" s="3" t="n">
-        <v>0</v>
+        <v>0.015212</v>
       </c>
       <c r="T34" s="3" t="n">
-        <v>0</v>
+        <v>0.128287</v>
       </c>
     </row>
     <row r="35">
@@ -2760,43 +2760,43 @@
         <v>4.537174</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.679516</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.269931</v>
+        <v>0.512072</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.068124</v>
+        <v>0.071951</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.587046</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.036196</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.020449</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>2.599062</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.77522</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.862851</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.184074</v>
       </c>
       <c r="R36" s="3" t="n">
-        <v>0</v>
+        <v>0.123135</v>
       </c>
       <c r="S36" s="3" t="n">
-        <v>0</v>
+        <v>0.015212</v>
       </c>
       <c r="T36" s="3" t="n">
-        <v>0</v>
+        <v>0.128287</v>
       </c>
     </row>
     <row r="37">
@@ -3552,43 +3552,43 @@
         <v>1.07186</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.708473</v>
+        <v>0.028957</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.261308</v>
+        <v>0.019167</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.006476</v>
+        <v>0.002649</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.63245</v>
+        <v>0.045404</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.048498</v>
+        <v>0.012302</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.025798</v>
+        <v>0.005349</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>2.69288</v>
+        <v>0.093818</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.786345</v>
+        <v>0.011125</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.8942099999999999</v>
+        <v>0.031359</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.343465</v>
+        <v>0.159391</v>
       </c>
       <c r="R48" s="3" t="n">
-        <v>0.130135</v>
+        <v>0.007</v>
       </c>
       <c r="S48" s="3" t="n">
-        <v>0.021862</v>
+        <v>0.00665</v>
       </c>
       <c r="T48" s="3" t="n">
-        <v>0.138845</v>
+        <v>0.010558</v>
       </c>
     </row>
     <row r="49">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11861,7 +11861,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -18552,7 +18552,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -20326,7 +20326,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -56478,7 +56478,7 @@
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
@@ -61552,7 +61552,7 @@
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E473" s="5" t="n">

--- a/output/pdf_financials_xlsx/AZR.xlsx
+++ b/output/pdf_financials_xlsx/AZR.xlsx
@@ -2217,10 +2217,10 @@
         <v>0</v>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0</v>
+        <v>0.087092</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0</v>
+        <v>0.077999</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0</v>
@@ -2281,10 +2281,10 @@
         <v>-7.07156</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-7.401549</v>
+        <v>-7.314457</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-6.128122</v>
+        <v>-6.050123</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-9.936159999999999</v>
@@ -7193,10 +7193,10 @@
         <v>0</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0</v>
+        <v>0.087092</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0</v>
+        <v>0.077999</v>
       </c>
       <c r="H100" s="3" t="n">
         <v>0</v>
@@ -40994,7 +40994,11 @@
           <t>Depreciation of property, plant and equipment</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
